--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125911651</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125912022</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -978,6 +978,889 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126013040</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>505963</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6846827</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126012902</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505993</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846813</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126013471</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>506052</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6846847</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126013182</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505972</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6846852</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126012885</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>505980</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6846844</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126013104</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506014</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6846841</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126012603</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>506032</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6846769</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126012780</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>505998</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6846819</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126012785</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505977</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6846829</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126013040</v>
+        <v>126012902</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505963</v>
+        <v>505993</v>
       </c>
       <c r="R5" t="n">
-        <v>6846827</v>
+        <v>6846813</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126012902</v>
+        <v>126013040</v>
       </c>
       <c r="B6" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505993</v>
+        <v>505963</v>
       </c>
       <c r="R6" t="n">
-        <v>6846813</v>
+        <v>6846827</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125911651</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125912022</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126012902</v>
+        <v>126013040</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505993</v>
+        <v>505963</v>
       </c>
       <c r="R5" t="n">
-        <v>6846813</v>
+        <v>6846827</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126013040</v>
+        <v>126012902</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505963</v>
+        <v>505993</v>
       </c>
       <c r="R6" t="n">
-        <v>6846827</v>
+        <v>6846813</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
         <v>126013182</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>126012885</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>126013104</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>126012603</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126012780</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126012785</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -1271,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126013182</v>
+        <v>126012885</v>
       </c>
       <c r="B8" t="n">
         <v>78972</v>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505972</v>
+        <v>505980</v>
       </c>
       <c r="R8" t="n">
-        <v>6846852</v>
+        <v>6846844</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126012885</v>
+        <v>126013182</v>
       </c>
       <c r="B9" t="n">
         <v>78972</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505980</v>
+        <v>505972</v>
       </c>
       <c r="R9" t="n">
-        <v>6846844</v>
+        <v>6846852</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -1271,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126012885</v>
+        <v>126013182</v>
       </c>
       <c r="B8" t="n">
         <v>78972</v>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505980</v>
+        <v>505972</v>
       </c>
       <c r="R8" t="n">
-        <v>6846844</v>
+        <v>6846852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126013182</v>
+        <v>126012885</v>
       </c>
       <c r="B9" t="n">
         <v>78972</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505972</v>
+        <v>505980</v>
       </c>
       <c r="R9" t="n">
-        <v>6846852</v>
+        <v>6846844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125911651</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125912022</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125924288</v>
       </c>
       <c r="B4" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>126013040</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>126012902</v>
       </c>
       <c r="B6" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>126013471</v>
       </c>
       <c r="B7" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>126013182</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>126012885</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>126013104</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>126012603</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126012780</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126012785</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125911651</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125912022</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125924288</v>
       </c>
       <c r="B4" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>126013040</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>126012902</v>
       </c>
       <c r="B6" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>126013471</v>
       </c>
       <c r="B7" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>126013182</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>126012885</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>126013104</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>126012603</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126012780</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126012785</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126013040</v>
+        <v>126012902</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505963</v>
+        <v>505993</v>
       </c>
       <c r="R5" t="n">
-        <v>6846827</v>
+        <v>6846813</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126012902</v>
+        <v>126013040</v>
       </c>
       <c r="B6" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505993</v>
+        <v>505963</v>
       </c>
       <c r="R6" t="n">
-        <v>6846813</v>
+        <v>6846827</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126012902</v>
+        <v>126013040</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505993</v>
+        <v>505963</v>
       </c>
       <c r="R5" t="n">
-        <v>6846813</v>
+        <v>6846827</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126013040</v>
+        <v>126012902</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505963</v>
+        <v>505993</v>
       </c>
       <c r="R6" t="n">
-        <v>6846827</v>
+        <v>6846813</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125911651</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125912022</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125924288</v>
       </c>
       <c r="B4" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126013040</v>
+        <v>126012902</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505963</v>
+        <v>505993</v>
       </c>
       <c r="R5" t="n">
-        <v>6846827</v>
+        <v>6846813</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126012902</v>
+        <v>126013040</v>
       </c>
       <c r="B6" t="n">
-        <v>57816</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505993</v>
+        <v>505963</v>
       </c>
       <c r="R6" t="n">
-        <v>6846813</v>
+        <v>6846827</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
         <v>126013471</v>
       </c>
       <c r="B7" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>126013182</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>126012885</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>126013104</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>126012603</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126012780</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126012785</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126012902</v>
+        <v>126013040</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505993</v>
+        <v>505963</v>
       </c>
       <c r="R5" t="n">
-        <v>6846813</v>
+        <v>6846827</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126013040</v>
+        <v>126012902</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505963</v>
+        <v>505993</v>
       </c>
       <c r="R6" t="n">
-        <v>6846827</v>
+        <v>6846813</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>134165208</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125911651</v>
+        <v>125911616</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505891</v>
+        <v>505925</v>
       </c>
       <c r="R2" t="n">
-        <v>6846773</v>
+        <v>6846740</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125912022</v>
+        <v>125911651</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505851</v>
+        <v>505891</v>
       </c>
       <c r="R3" t="n">
-        <v>6846911</v>
+        <v>6846773</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,57 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125924288</v>
+        <v>125912022</v>
       </c>
       <c r="B4" t="n">
-        <v>56840</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ryggskog, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506049</v>
+        <v>505851</v>
       </c>
       <c r="R4" t="n">
-        <v>6846790</v>
+        <v>6846911</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Höna och kyckling.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126013040</v>
+        <v>126012549</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1011,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505963</v>
+        <v>506154</v>
       </c>
       <c r="R5" t="n">
-        <v>6846827</v>
+        <v>6846771</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,60 +1051,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126012902</v>
+        <v>126012585</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505993</v>
+        <v>506129</v>
       </c>
       <c r="R6" t="n">
-        <v>6846813</v>
+        <v>6846826</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1145,9 +1131,19 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1162,60 +1158,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126013471</v>
+        <v>126012603</v>
       </c>
       <c r="B7" t="n">
-        <v>56840</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506052</v>
+        <v>506032</v>
       </c>
       <c r="R7" t="n">
-        <v>6846847</v>
+        <v>6846769</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,26 +1255,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126013182</v>
+        <v>126012780</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1302,17 +1298,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505972</v>
+        <v>505998</v>
       </c>
       <c r="R8" t="n">
-        <v>6846852</v>
+        <v>6846819</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1356,26 +1352,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126012885</v>
+        <v>126012785</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1403,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505980</v>
+        <v>505977</v>
       </c>
       <c r="R9" t="n">
-        <v>6846844</v>
+        <v>6846829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,14 +1461,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126013104</v>
+        <v>126012885</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1496,17 +1492,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506014</v>
+        <v>505980</v>
       </c>
       <c r="R10" t="n">
-        <v>6846841</v>
+        <v>6846844</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1533,19 +1529,9 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1560,26 +1546,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126012603</v>
+        <v>126013040</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1607,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506032</v>
+        <v>505963</v>
       </c>
       <c r="R11" t="n">
-        <v>6846769</v>
+        <v>6846827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,14 +1655,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126012780</v>
+        <v>126013104</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1700,17 +1686,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505998</v>
+        <v>506014</v>
       </c>
       <c r="R12" t="n">
-        <v>6846819</v>
+        <v>6846841</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1737,9 +1723,19 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1754,26 +1750,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126012785</v>
+        <v>126013182</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1801,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505977</v>
+        <v>505972</v>
       </c>
       <c r="R13" t="n">
-        <v>6846829</v>
+        <v>6846852</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,14 +1859,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134165208</v>
+        <v>134165118</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1960,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134165020</v>
+        <v>125924288</v>
       </c>
       <c r="B15" t="n">
-        <v>58658</v>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,16 +1967,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1988,25 +1984,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505921</v>
+        <v>506049</v>
       </c>
       <c r="R15" t="n">
-        <v>6846855</v>
+        <v>6846790</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2030,12 +2030,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Höna och kyckling.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2059,6 +2064,302 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126013471</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506052</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6846847</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126012902</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>505993</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6846813</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134165020</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>505921</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6846855</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28866-2025 artfynd.xlsx
+++ b/artfynd/A 28866-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125911616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125911651</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125912022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012585</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012603</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012780</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012785</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126013040</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126013104</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126013182</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165118</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2064,6 +2134,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125924288</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126013471</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012902</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2360,8 +2445,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165020</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>